--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -5,18 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00084566-794C-4780-B9F3-525F016FACEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D969643-B5E1-4F91-A934-B932115A8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="X" sheetId="1" r:id="rId1"/>
+    <sheet name="Y" sheetId="2" r:id="rId2"/>
+    <sheet name="XY" sheetId="3" r:id="rId3"/>
+    <sheet name="W" sheetId="4" r:id="rId4"/>
+    <sheet name="XYW" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">W!$A$4:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">X!$A$4:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XY!$A$4:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">XYW!$A$4:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Y!$A$4:$A$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
   <si>
     <t>Leg</t>
   </si>
@@ -72,6 +80,18 @@
   </si>
   <si>
     <t>Lf_z</t>
+  </si>
+  <si>
+    <t>Vx:</t>
+  </si>
+  <si>
+    <t>Vy:</t>
+  </si>
+  <si>
+    <t>Vm:</t>
+  </si>
+  <si>
+    <t>Wz:</t>
   </si>
 </sst>
 </file>
@@ -147,10 +167,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.5793974957211956E-2"/>
-          <c:y val="2.3523120179402099E-2"/>
-          <c:w val="0.94448318210702975"/>
-          <c:h val="0.95295375964119577"/>
+          <c:x val="4.2605375422101736E-2"/>
+          <c:y val="2.3523236066079974E-2"/>
+          <c:w val="0.93042691546865974"/>
+          <c:h val="0.89865512286077365"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -161,7 +181,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>X!$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -194,34 +214,34 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$7</c:f>
+              <c:f>X!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>238.66</c:v>
+                  <c:v>182.41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.75</c:v>
+                  <c:v>-52.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-231.16</c:v>
+                  <c:v>-287.41000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-231.16</c:v>
+                  <c:v>-287.41000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.75</c:v>
+                  <c:v>-52.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>238.66</c:v>
+                  <c:v>182.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$7</c:f>
+              <c:f>X!$C$5:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -283,34 +303,34 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$7</c:f>
+              <c:f>X!$E$5:$E$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>231.16</c:v>
+                  <c:v>287.41000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3.75</c:v>
+                  <c:v>52.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-238.66</c:v>
+                  <c:v>-182.41</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-238.66</c:v>
+                  <c:v>-182.41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.75</c:v>
+                  <c:v>52.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>231.16</c:v>
+                  <c:v>287.41000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$7</c:f>
+              <c:f>X!$F$5:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -372,7 +392,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$7</c:f>
+              <c:f>X!$H$5:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -399,7 +419,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$2:$I$7</c:f>
+              <c:f>X!$I$5:$I$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -463,6 +483,73 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47870735244800422"/>
+              <c:y val="0.9312281326825097"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -525,6 +612,2681 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="6.0490772461377403E-3"/>
+              <c:y val="0.42931390363534883"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016859711"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.2605375422101736E-2"/>
+          <c:y val="2.3523236066079974E-2"/>
+          <c:w val="0.93042691546865974"/>
+          <c:h val="0.89865512286077365"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Y!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>St_y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Y!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Y!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>116.88</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>252.51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>116.88</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-154.38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-290.01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-154.38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E6A8-46BF-B2AC-C88139B44B87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Sw</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Y!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Y!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>154.38</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>290.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-116.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-252.51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-116.88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E6A8-46BF-B2AC-C88139B44B87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lf</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Y!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Y!$I$5:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E6A8-46BF-B2AC-C88139B44B87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1016859711"/>
+        <c:axId val="1115486639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1016859711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47870735244800422"/>
+              <c:y val="0.9312281326825097"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115486639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1115486639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="6.0490772461377403E-3"/>
+              <c:y val="0.42931390363534883"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016859711"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.2605375422101736E-2"/>
+          <c:y val="2.3523236066079974E-2"/>
+          <c:w val="0.93042691546865974"/>
+          <c:h val="0.89865512286077365"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>XY!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>St_y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XY!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>208.66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-26.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-261.16000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-261.16000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-26.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>208.66</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XY!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>109.38</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>245.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>109.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-161.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-297.51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-161.88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-91FC-4D7D-934F-07F608CA0A5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Sw</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XY!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>261.16000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-208.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-208.66</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>261.16000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XY!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>161.88</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>297.51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>161.88</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-109.38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-245.01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-109.38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-91FC-4D7D-934F-07F608CA0A5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lf</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XY!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XY!$I$5:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-91FC-4D7D-934F-07F608CA0A5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1016859711"/>
+        <c:axId val="1115486639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1016859711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47870735244800422"/>
+              <c:y val="0.9312281326825097"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115486639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1115486639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="6.0490772461377403E-3"/>
+              <c:y val="0.42931390363534883"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016859711"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.2605375422101736E-2"/>
+          <c:y val="2.3523236066079974E-2"/>
+          <c:w val="0.93042691546865974"/>
+          <c:h val="0.89865512286077365"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>W!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>St_y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>W!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>247.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25.43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-222.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-247.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-25.43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>222.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>W!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>113.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>157.65</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-113.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-157.65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-91BD-45F2-9204-9E8D1E164920}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Sw</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>W!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>222.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-25.43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-247.63</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-222.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>247.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>W!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>157.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>113.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-157.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-113.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-91BD-45F2-9204-9E8D1E164920}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lf</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>W!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>W!$I$5:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-91BD-45F2-9204-9E8D1E164920}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1016859711"/>
+        <c:axId val="1115486639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1016859711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47870735244800422"/>
+              <c:y val="0.9312281326825097"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115486639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1115486639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="6.0490772461377403E-3"/>
+              <c:y val="0.42931390363534883"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016859711"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.2605375422101736E-2"/>
+          <c:y val="2.3523236066079974E-2"/>
+          <c:w val="0.93042691546865974"/>
+          <c:h val="0.89865512286077365"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>XYW!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>St_y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XYW!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>236.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-233.58</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-243.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-13.92</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>226.08</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XYW!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>123.07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>267.51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>140.69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-130.57</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-275.01</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-148.19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FA69-4F64-9095-30C126BF2999}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Sw</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XYW!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>233.58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-236.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-226.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.92</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>243.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XYW!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>148.19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>275.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>130.57</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-140.69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-267.51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-123.07</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FA69-4F64-9095-30C126BF2999}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lf</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>XYW!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>234.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-234.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>XYW!$I$5:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>271.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135.63</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-271.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-135.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FA69-4F64-9095-30C126BF2999}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1016859711"/>
+        <c:axId val="1115486639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1016859711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47870735244800422"/>
+              <c:y val="0.9312281326825097"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115486639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1115486639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Y Axis</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="6.0490772461377403E-3"/>
+              <c:y val="0.42931390363534883"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -689,7 +3451,2231 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1211,14 +6197,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1230,6 +6216,178 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314372DE-435B-434C-9286-6166DF0C1B4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52D6BF6F-E380-408F-9421-4F8F78A0DA27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B63ED0DC-0A8D-4EAC-893A-3B9C35AF5E84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34A592F8-FD65-4ABC-936D-2B7D60BBEE47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1563,39 +6721,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2FE928-1AFB-4FD0-9234-9A0A25EB1FB5}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>140</v>
+      </c>
+      <c r="B2">
         <v>0</v>
       </c>
+      <c r="C2">
+        <v>140</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>182.41</v>
+      </c>
+      <c r="C5">
+        <v>135.63</v>
+      </c>
+      <c r="D5">
+        <v>-63.63</v>
+      </c>
+      <c r="E5">
+        <v>287.41000000000003</v>
+      </c>
+      <c r="F5">
+        <v>135.63</v>
+      </c>
+      <c r="G5">
+        <v>-63.63</v>
+      </c>
+      <c r="H5">
+        <v>234.91</v>
+      </c>
+      <c r="I5">
+        <v>135.63</v>
+      </c>
+      <c r="J5">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>-52.5</v>
+      </c>
+      <c r="C6">
+        <v>271.26</v>
+      </c>
+      <c r="D6">
+        <v>-63.63</v>
+      </c>
+      <c r="E6">
+        <v>52.5</v>
+      </c>
+      <c r="F6">
+        <v>271.26</v>
+      </c>
+      <c r="G6">
+        <v>-63.63</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>271.26</v>
+      </c>
+      <c r="J6">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>-287.41000000000003</v>
+      </c>
+      <c r="C7">
+        <v>135.63</v>
+      </c>
+      <c r="D7">
+        <v>-63.63</v>
+      </c>
+      <c r="E7">
+        <v>-182.41</v>
+      </c>
+      <c r="F7">
+        <v>135.63</v>
+      </c>
+      <c r="G7">
+        <v>-63.63</v>
+      </c>
+      <c r="H7">
+        <v>-234.91</v>
+      </c>
+      <c r="I7">
+        <v>135.63</v>
+      </c>
+      <c r="J7">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-287.41000000000003</v>
+      </c>
+      <c r="C8">
+        <v>-135.63</v>
+      </c>
+      <c r="D8">
+        <v>-63.63</v>
+      </c>
+      <c r="E8">
+        <v>-182.41</v>
+      </c>
+      <c r="F8">
+        <v>-135.63</v>
+      </c>
+      <c r="G8">
+        <v>-63.63</v>
+      </c>
+      <c r="H8">
+        <v>-234.91</v>
+      </c>
+      <c r="I8">
+        <v>-135.63</v>
+      </c>
+      <c r="J8">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>-52.5</v>
+      </c>
+      <c r="C9">
+        <v>-271.26</v>
+      </c>
+      <c r="D9">
+        <v>-63.63</v>
+      </c>
+      <c r="E9">
+        <v>52.5</v>
+      </c>
+      <c r="F9">
+        <v>-271.26</v>
+      </c>
+      <c r="G9">
+        <v>-63.63</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-271.26</v>
+      </c>
+      <c r="J9">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>182.41</v>
+      </c>
+      <c r="C10">
+        <v>-135.63</v>
+      </c>
+      <c r="D10">
+        <v>-63.63</v>
+      </c>
+      <c r="E10">
+        <v>287.41000000000003</v>
+      </c>
+      <c r="F10">
+        <v>-135.63</v>
+      </c>
+      <c r="G10">
+        <v>-63.63</v>
+      </c>
+      <c r="H10">
+        <v>234.91</v>
+      </c>
+      <c r="I10">
+        <v>-135.63</v>
+      </c>
+      <c r="J10">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82731D4-04A4-4FF3-BF80-2BE78F95CA60}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1603,147 +7006,97 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>238.66</v>
+        <v>50</v>
       </c>
       <c r="C2">
-        <v>135.63</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>-63.63</v>
-      </c>
-      <c r="E2">
-        <v>231.16</v>
-      </c>
-      <c r="F2">
-        <v>135.63</v>
-      </c>
-      <c r="G2">
-        <v>-63.63</v>
-      </c>
-      <c r="H2">
-        <v>234.91</v>
-      </c>
-      <c r="I2">
-        <v>135.63</v>
-      </c>
-      <c r="J2">
-        <v>-51.63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>271.26</v>
-      </c>
-      <c r="D3">
-        <v>-63.63</v>
-      </c>
-      <c r="E3">
-        <v>-3.75</v>
-      </c>
-      <c r="F3">
-        <v>271.26</v>
-      </c>
-      <c r="G3">
-        <v>-63.63</v>
-      </c>
-      <c r="H3">
         <v>0</v>
-      </c>
-      <c r="I3">
-        <v>271.26</v>
-      </c>
-      <c r="J3">
-        <v>-51.63</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>-231.16</v>
-      </c>
-      <c r="C4">
-        <v>135.63</v>
-      </c>
-      <c r="D4">
-        <v>-63.63</v>
-      </c>
-      <c r="E4">
-        <v>-238.66</v>
-      </c>
-      <c r="F4">
-        <v>135.63</v>
-      </c>
-      <c r="G4">
-        <v>-63.63</v>
-      </c>
-      <c r="H4">
-        <v>-234.91</v>
-      </c>
-      <c r="I4">
-        <v>135.63</v>
-      </c>
-      <c r="J4">
-        <v>-51.63</v>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>-231.16</v>
+        <v>234.91</v>
       </c>
       <c r="C5">
-        <v>-135.63</v>
+        <v>116.88</v>
       </c>
       <c r="D5">
         <v>-63.63</v>
       </c>
       <c r="E5">
-        <v>-238.66</v>
+        <v>234.91</v>
       </c>
       <c r="F5">
-        <v>-135.63</v>
+        <v>154.38</v>
       </c>
       <c r="G5">
         <v>-63.63</v>
       </c>
       <c r="H5">
-        <v>-234.91</v>
+        <v>234.91</v>
       </c>
       <c r="I5">
-        <v>-135.63</v>
+        <v>135.63</v>
       </c>
       <c r="J5">
-        <v>-51.63</v>
+        <v>-8.6300000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-271.26</v>
+        <v>252.51</v>
       </c>
       <c r="D6">
         <v>-63.63</v>
       </c>
       <c r="E6">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>-271.26</v>
+        <v>290.01</v>
       </c>
       <c r="G6">
         <v>-63.63</v>
@@ -1752,42 +7105,927 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-271.26</v>
+        <v>271.26</v>
       </c>
       <c r="J6">
-        <v>-51.63</v>
+        <v>-8.6300000000000008</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>238.66</v>
+        <v>-234.91</v>
       </c>
       <c r="C7">
-        <v>-135.63</v>
+        <v>116.88</v>
       </c>
       <c r="D7">
         <v>-63.63</v>
       </c>
       <c r="E7">
-        <v>231.16</v>
+        <v>-234.91</v>
       </c>
       <c r="F7">
-        <v>-135.63</v>
+        <v>154.38</v>
       </c>
       <c r="G7">
         <v>-63.63</v>
       </c>
       <c r="H7">
+        <v>-234.91</v>
+      </c>
+      <c r="I7">
+        <v>135.63</v>
+      </c>
+      <c r="J7">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-234.91</v>
+      </c>
+      <c r="C8">
+        <v>-154.38</v>
+      </c>
+      <c r="D8">
+        <v>-63.63</v>
+      </c>
+      <c r="E8">
+        <v>-234.91</v>
+      </c>
+      <c r="F8">
+        <v>-116.88</v>
+      </c>
+      <c r="G8">
+        <v>-63.63</v>
+      </c>
+      <c r="H8">
+        <v>-234.91</v>
+      </c>
+      <c r="I8">
+        <v>-135.63</v>
+      </c>
+      <c r="J8">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>-290.01</v>
+      </c>
+      <c r="D9">
+        <v>-63.63</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>-252.51</v>
+      </c>
+      <c r="G9">
+        <v>-63.63</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-271.26</v>
+      </c>
+      <c r="J9">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
         <v>234.91</v>
       </c>
+      <c r="C10">
+        <v>-154.38</v>
+      </c>
+      <c r="D10">
+        <v>-63.63</v>
+      </c>
+      <c r="E10">
+        <v>234.91</v>
+      </c>
+      <c r="F10">
+        <v>-116.88</v>
+      </c>
+      <c r="G10">
+        <v>-63.63</v>
+      </c>
+      <c r="H10">
+        <v>234.91</v>
+      </c>
+      <c r="I10">
+        <v>-135.63</v>
+      </c>
+      <c r="J10">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6FC07D-3936-4796-AFC6-66879CDE30D8}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>70</v>
+      </c>
+      <c r="B2">
+        <v>70</v>
+      </c>
+      <c r="C2">
+        <v>98.99</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>208.66</v>
+      </c>
+      <c r="C5">
+        <v>109.38</v>
+      </c>
+      <c r="D5">
+        <v>-63.63</v>
+      </c>
+      <c r="E5">
+        <v>261.16000000000003</v>
+      </c>
+      <c r="F5">
+        <v>161.88</v>
+      </c>
+      <c r="G5">
+        <v>-63.63</v>
+      </c>
+      <c r="H5">
+        <v>234.91</v>
+      </c>
+      <c r="I5">
+        <v>135.63</v>
+      </c>
+      <c r="J5">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>-26.25</v>
+      </c>
+      <c r="C6">
+        <v>245.01</v>
+      </c>
+      <c r="D6">
+        <v>-63.63</v>
+      </c>
+      <c r="E6">
+        <v>26.25</v>
+      </c>
+      <c r="F6">
+        <v>297.51</v>
+      </c>
+      <c r="G6">
+        <v>-63.63</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>271.26</v>
+      </c>
+      <c r="J6">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>-261.16000000000003</v>
+      </c>
+      <c r="C7">
+        <v>109.38</v>
+      </c>
+      <c r="D7">
+        <v>-63.63</v>
+      </c>
+      <c r="E7">
+        <v>-208.66</v>
+      </c>
+      <c r="F7">
+        <v>161.88</v>
+      </c>
+      <c r="G7">
+        <v>-63.63</v>
+      </c>
+      <c r="H7">
+        <v>-234.91</v>
+      </c>
       <c r="I7">
+        <v>135.63</v>
+      </c>
+      <c r="J7">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-261.16000000000003</v>
+      </c>
+      <c r="C8">
+        <v>-161.88</v>
+      </c>
+      <c r="D8">
+        <v>-63.63</v>
+      </c>
+      <c r="E8">
+        <v>-208.66</v>
+      </c>
+      <c r="F8">
+        <v>-109.38</v>
+      </c>
+      <c r="G8">
+        <v>-63.63</v>
+      </c>
+      <c r="H8">
+        <v>-234.91</v>
+      </c>
+      <c r="I8">
         <v>-135.63</v>
       </c>
+      <c r="J8">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>-26.25</v>
+      </c>
+      <c r="C9">
+        <v>-297.51</v>
+      </c>
+      <c r="D9">
+        <v>-63.63</v>
+      </c>
+      <c r="E9">
+        <v>26.25</v>
+      </c>
+      <c r="F9">
+        <v>-245.01</v>
+      </c>
+      <c r="G9">
+        <v>-63.63</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-271.26</v>
+      </c>
+      <c r="J9">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>208.66</v>
+      </c>
+      <c r="C10">
+        <v>-161.88</v>
+      </c>
+      <c r="D10">
+        <v>-63.63</v>
+      </c>
+      <c r="E10">
+        <v>261.16000000000003</v>
+      </c>
+      <c r="F10">
+        <v>-109.38</v>
+      </c>
+      <c r="G10">
+        <v>-63.63</v>
+      </c>
+      <c r="H10">
+        <v>234.91</v>
+      </c>
+      <c r="I10">
+        <v>-135.63</v>
+      </c>
+      <c r="J10">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78506E60-2C92-4E37-B662-D65BDC95D41A}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>247.63</v>
+      </c>
+      <c r="C5">
+        <v>113.6</v>
+      </c>
+      <c r="D5">
+        <v>-63.63</v>
+      </c>
+      <c r="E5">
+        <v>222.2</v>
+      </c>
+      <c r="F5">
+        <v>157.65</v>
+      </c>
+      <c r="G5">
+        <v>-63.63</v>
+      </c>
+      <c r="H5">
+        <v>234.91</v>
+      </c>
+      <c r="I5">
+        <v>135.63</v>
+      </c>
+      <c r="J5">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>25.43</v>
+      </c>
+      <c r="C6">
+        <v>271.26</v>
+      </c>
+      <c r="D6">
+        <v>-63.63</v>
+      </c>
+      <c r="E6">
+        <v>-25.43</v>
+      </c>
+      <c r="F6">
+        <v>271.26</v>
+      </c>
+      <c r="G6">
+        <v>-63.63</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>271.26</v>
+      </c>
+      <c r="J6">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>-222.2</v>
+      </c>
+      <c r="C7">
+        <v>157.65</v>
+      </c>
+      <c r="D7">
+        <v>-63.63</v>
+      </c>
+      <c r="E7">
+        <v>-247.63</v>
+      </c>
+      <c r="F7">
+        <v>113.6</v>
+      </c>
+      <c r="G7">
+        <v>-63.63</v>
+      </c>
+      <c r="H7">
+        <v>-234.91</v>
+      </c>
+      <c r="I7">
+        <v>135.63</v>
+      </c>
       <c r="J7">
-        <v>-51.63</v>
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-247.63</v>
+      </c>
+      <c r="C8">
+        <v>-113.6</v>
+      </c>
+      <c r="D8">
+        <v>-63.63</v>
+      </c>
+      <c r="E8">
+        <v>-222.2</v>
+      </c>
+      <c r="F8">
+        <v>-157.65</v>
+      </c>
+      <c r="G8">
+        <v>-63.63</v>
+      </c>
+      <c r="H8">
+        <v>-234.91</v>
+      </c>
+      <c r="I8">
+        <v>-135.63</v>
+      </c>
+      <c r="J8">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>-25.43</v>
+      </c>
+      <c r="C9">
+        <v>-271.26</v>
+      </c>
+      <c r="D9">
+        <v>-63.63</v>
+      </c>
+      <c r="E9">
+        <v>25.43</v>
+      </c>
+      <c r="F9">
+        <v>-271.26</v>
+      </c>
+      <c r="G9">
+        <v>-63.63</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-271.26</v>
+      </c>
+      <c r="J9">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>222.2</v>
+      </c>
+      <c r="C10">
+        <v>-157.65</v>
+      </c>
+      <c r="D10">
+        <v>-63.63</v>
+      </c>
+      <c r="E10">
+        <v>247.63</v>
+      </c>
+      <c r="F10">
+        <v>-113.6</v>
+      </c>
+      <c r="G10">
+        <v>-63.63</v>
+      </c>
+      <c r="H10">
+        <v>234.91</v>
+      </c>
+      <c r="I10">
+        <v>-135.63</v>
+      </c>
+      <c r="J10">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF143BA2-DD69-45E4-B428-8B806A230E52}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>14.14</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>236.25</v>
+      </c>
+      <c r="C5">
+        <v>123.07</v>
+      </c>
+      <c r="D5">
+        <v>-63.63</v>
+      </c>
+      <c r="E5">
+        <v>233.58</v>
+      </c>
+      <c r="F5">
+        <v>148.19</v>
+      </c>
+      <c r="G5">
+        <v>-63.63</v>
+      </c>
+      <c r="H5">
+        <v>234.91</v>
+      </c>
+      <c r="I5">
+        <v>135.63</v>
+      </c>
+      <c r="J5">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6.42</v>
+      </c>
+      <c r="C6">
+        <v>267.51</v>
+      </c>
+      <c r="D6">
+        <v>-63.63</v>
+      </c>
+      <c r="E6">
+        <v>-6.42</v>
+      </c>
+      <c r="F6">
+        <v>275.01</v>
+      </c>
+      <c r="G6">
+        <v>-63.63</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>271.26</v>
+      </c>
+      <c r="J6">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>-233.58</v>
+      </c>
+      <c r="C7">
+        <v>140.69</v>
+      </c>
+      <c r="D7">
+        <v>-63.63</v>
+      </c>
+      <c r="E7">
+        <v>-236.25</v>
+      </c>
+      <c r="F7">
+        <v>130.57</v>
+      </c>
+      <c r="G7">
+        <v>-63.63</v>
+      </c>
+      <c r="H7">
+        <v>-234.91</v>
+      </c>
+      <c r="I7">
+        <v>135.63</v>
+      </c>
+      <c r="J7">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>-243.75</v>
+      </c>
+      <c r="C8">
+        <v>-130.57</v>
+      </c>
+      <c r="D8">
+        <v>-63.63</v>
+      </c>
+      <c r="E8">
+        <v>-226.08</v>
+      </c>
+      <c r="F8">
+        <v>-140.69</v>
+      </c>
+      <c r="G8">
+        <v>-63.63</v>
+      </c>
+      <c r="H8">
+        <v>-234.91</v>
+      </c>
+      <c r="I8">
+        <v>-135.63</v>
+      </c>
+      <c r="J8">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>-13.92</v>
+      </c>
+      <c r="C9">
+        <v>-275.01</v>
+      </c>
+      <c r="D9">
+        <v>-63.63</v>
+      </c>
+      <c r="E9">
+        <v>13.92</v>
+      </c>
+      <c r="F9">
+        <v>-267.51</v>
+      </c>
+      <c r="G9">
+        <v>-63.63</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-271.26</v>
+      </c>
+      <c r="J9">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>226.08</v>
+      </c>
+      <c r="C10">
+        <v>-148.19</v>
+      </c>
+      <c r="D10">
+        <v>-63.63</v>
+      </c>
+      <c r="E10">
+        <v>243.75</v>
+      </c>
+      <c r="F10">
+        <v>-123.07</v>
+      </c>
+      <c r="G10">
+        <v>-63.63</v>
+      </c>
+      <c r="H10">
+        <v>234.91</v>
+      </c>
+      <c r="I10">
+        <v>-135.63</v>
+      </c>
+      <c r="J10">
+        <v>-8.6300000000000008</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D969643-B5E1-4F91-A934-B932115A8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD79CC9-FD29-43FC-9CF6-10D8D0DE317A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="XY" sheetId="3" r:id="rId3"/>
     <sheet name="W" sheetId="4" r:id="rId4"/>
     <sheet name="XYW" sheetId="5" r:id="rId5"/>
+    <sheet name="RC Calculations" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">W!$A$4:$A$10</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="59">
   <si>
     <t>Leg</t>
   </si>
@@ -93,13 +94,156 @@
   <si>
     <t>Wz:</t>
   </si>
+  <si>
+    <t>Constants</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit </t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>PI/6</t>
+  </si>
+  <si>
+    <t>PI/3</t>
+  </si>
+  <si>
+    <t>rad</t>
+  </si>
+  <si>
+    <t>Calculations</t>
+  </si>
+  <si>
+    <t>ADC MAX</t>
+  </si>
+  <si>
+    <t>X ADC Max</t>
+  </si>
+  <si>
+    <t>Y ADC Max</t>
+  </si>
+  <si>
+    <t>V mag min</t>
+  </si>
+  <si>
+    <t>V mag max</t>
+  </si>
+  <si>
+    <t>X ADC Mid</t>
+  </si>
+  <si>
+    <t>Y ADC Mid</t>
+  </si>
+  <si>
+    <t>ADC MIN</t>
+  </si>
+  <si>
+    <t>bits</t>
+  </si>
+  <si>
+    <t>mm/s</t>
+  </si>
+  <si>
+    <t>ADC X</t>
+  </si>
+  <si>
+    <t>ADC Y</t>
+  </si>
+  <si>
+    <t>V map</t>
+  </si>
+  <si>
+    <t>V adc</t>
+  </si>
+  <si>
+    <t>ADC XC</t>
+  </si>
+  <si>
+    <t>ADC YC</t>
+  </si>
+  <si>
+    <t>X ADC Min</t>
+  </si>
+  <si>
+    <t>Y ADC Min</t>
+  </si>
+  <si>
+    <t>Center Shift</t>
+  </si>
+  <si>
+    <t>X ADC MaxS</t>
+  </si>
+  <si>
+    <t>X ADC MinS</t>
+  </si>
+  <si>
+    <t>Y ADC MaxS</t>
+  </si>
+  <si>
+    <t>Y ADC MinS</t>
+  </si>
+  <si>
+    <t>V adc Max</t>
+  </si>
+  <si>
+    <t>V adc Min</t>
+  </si>
+  <si>
+    <t>Theta T1</t>
+  </si>
+  <si>
+    <t>Theta T2</t>
+  </si>
+  <si>
+    <t>Quantized</t>
+  </si>
+  <si>
+    <t>Theta T2D</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>vx</t>
+  </si>
+  <si>
+    <t>vy</t>
+  </si>
+  <si>
+    <t>along robot +X</t>
+  </si>
+  <si>
+    <t>along robot +Y</t>
+  </si>
+  <si>
+    <t>V clamp</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -115,7 +259,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,12 +267,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8032,4 +8261,440 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E776AA44-A3C8-43E7-96F1-C4D35D29F60B}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <f>PI()/6</f>
+        <v>0.52359877559829882</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4095</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <f>PI()/3</f>
+        <v>1.0471975511965976</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4095</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2">
+        <f>G3-B14</f>
+        <v>2048</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2">
+        <f>G4-B16</f>
+        <v>953</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1958</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="2">
+        <f>SQRT(G5*G5+G6*G6)</f>
+        <v>2258.8742771566549</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1958</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2">
+        <f>(G7)*((B21-B20)/(B18-B19))+B20</f>
+        <v>154.41523379000571</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <f>B5-B7</f>
+        <v>2137</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="2">
+        <f>IF(G8&gt;B21, B21,G8)</f>
+        <v>140</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2">
+        <f>B5-B8</f>
+        <v>2137</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="2">
+        <f>ATAN2(G5,G6)</f>
+        <v>0.43553063969993661</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="2">
+        <f>B6-B7</f>
+        <v>-1958</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="2">
+        <f>B4*ROUND(G10/B4, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2">
+        <f>B6-B8</f>
+        <v>-1958</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="2">
+        <f>DEGREES(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2">
+        <v>90</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="2">
+        <f>G9*COS(G11)</f>
+        <v>140</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2">
+        <f>B9-B13</f>
+        <v>2047</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="2">
+        <f>G9*SIN(G11)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2">
+        <f>B11-B13</f>
+        <v>-2048</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2">
+        <f>B14</f>
+        <v>2047</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2">
+        <f>B15</f>
+        <v>-2048</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2048</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2">
+        <v>140</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD79CC9-FD29-43FC-9CF6-10D8D0DE317A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2F866A-B2F8-449B-A2F3-0D24835391C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="W" sheetId="4" r:id="rId4"/>
     <sheet name="XYW" sheetId="5" r:id="rId5"/>
     <sheet name="RC Calculations" sheetId="6" r:id="rId6"/>
+    <sheet name="Ripple Phase" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">W!$A$4:$A$10</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="71">
   <si>
     <t>Leg</t>
   </si>
@@ -229,6 +230,42 @@
   <si>
     <t>test</t>
   </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>Leg 0</t>
+  </si>
+  <si>
+    <t>Leg 1</t>
+  </si>
+  <si>
+    <t>Leg 2</t>
+  </si>
+  <si>
+    <t>Leg 3</t>
+  </si>
+  <si>
+    <t>Leg 4</t>
+  </si>
+  <si>
+    <t>Leg 5</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Cycle Const</t>
+  </si>
+  <si>
+    <t>s_total</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
@@ -344,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -358,6 +395,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8697,4 +8739,186 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AFBAB9-467F-4E05-A5CF-E22C3165A618}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="2">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="F3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <f>$B$5-(ABS(G4-$B$4)*$B$3)</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <f>$B$5-(ABS(G5-$B$4)*$B$3)</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <f>$B$5-(ABS(G6-$B$4)*$B$3)</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <f>$B$5-(ABS(G7-$B$4)*$B$3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2">
+        <f>$B$5-(ABS(G8-$B$4)*$B$3)</f>
+        <v>0.33333333333333337</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2">
+        <f>$B$5-(ABS(G9-$B$4)*$B$3)</f>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2F866A-B2F8-449B-A2F3-0D24835391C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CA9DB3-D65D-4D4D-B55D-3B0D7CF09910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
@@ -8743,7 +8743,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AFBAB9-467F-4E05-A5CF-E22C3165A618}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -8751,7 +8751,7 @@
     <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -8766,7 +8766,7 @@
       <c r="H1" s="5"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
@@ -8816,12 +8816,12 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -8834,12 +8834,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
+        <f>IF(($B$4-G4)&lt;=0,$B$5-(ABS(G4-$B$4)*$B$3), (ABS(G4-$B$4)*$B$3))</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="K4">
         <f>$B$5-(ABS(G4-$B$4)*$B$3)</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="2"/>
+        <v>0.66666666666666674</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>68</v>
       </c>
@@ -8857,12 +8861,12 @@
         <v>1</v>
       </c>
       <c r="H5" s="2">
-        <f>$B$5-(ABS(G5-$B$4)*$B$3)</f>
-        <v>0.83333333333333337</v>
+        <f t="shared" ref="H5:H9" si="0">IF(($B$4-G5)&lt;=0,$B$5-(ABS(G5-$B$4)*$B$3), (ABS(G5-$B$4)*$B$3))</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
@@ -8870,12 +8874,12 @@
         <v>2</v>
       </c>
       <c r="H6" s="2">
-        <f>$B$5-(ABS(G6-$B$4)*$B$3)</f>
-        <v>0.66666666666666674</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
@@ -8883,12 +8887,12 @@
         <v>3</v>
       </c>
       <c r="H7" s="2">
-        <f>$B$5-(ABS(G7-$B$4)*$B$3)</f>
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F8" s="2" t="s">
         <v>61</v>
       </c>
@@ -8896,12 +8900,12 @@
         <v>4</v>
       </c>
       <c r="H8" s="2">
-        <f>$B$5-(ABS(G8-$B$4)*$B$3)</f>
-        <v>0.33333333333333337</v>
+        <f t="shared" si="0"/>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F9" s="2" t="s">
         <v>63</v>
       </c>
@@ -8909,8 +8913,8 @@
         <v>5</v>
       </c>
       <c r="H9" s="2">
-        <f>$B$5-(ABS(G9-$B$4)*$B$3)</f>
-        <v>0.16666666666666674</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="I9" s="2"/>
     </row>

--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A94399-F0F9-444D-B350-275B96F5405C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F774419-B06F-4706-9248-32F96172EE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="1" r:id="rId1"/>
@@ -538,22 +538,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>182.41</c:v>
+                  <c:v>199.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-52.5</c:v>
+                  <c:v>-41.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-287.41000000000003</c:v>
+                  <c:v>-281.82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-287.41000000000003</c:v>
+                  <c:v>-281.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-52.5</c:v>
+                  <c:v>-41.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>182.41</c:v>
+                  <c:v>199.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -565,22 +565,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>135.63</c:v>
+                  <c:v>138.88999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>271.26</c:v>
+                  <c:v>277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135.63</c:v>
+                  <c:v>138.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-271.26</c:v>
+                  <c:v>-277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -627,22 +627,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>287.41000000000003</c:v>
+                  <c:v>281.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.5</c:v>
+                  <c:v>41.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-182.41</c:v>
+                  <c:v>-199.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-182.41</c:v>
+                  <c:v>-199.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52.5</c:v>
+                  <c:v>41.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>287.41000000000003</c:v>
+                  <c:v>281.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -654,22 +654,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>135.63</c:v>
+                  <c:v>138.88999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>271.26</c:v>
+                  <c:v>277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135.63</c:v>
+                  <c:v>138.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-271.26</c:v>
+                  <c:v>-277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -716,22 +716,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>234.91</c:v>
+                  <c:v>240.57</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-234.91</c:v>
+                  <c:v>-240.57</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-234.91</c:v>
+                  <c:v>-240.57</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>234.91</c:v>
+                  <c:v>240.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -743,22 +743,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>135.63</c:v>
+                  <c:v>138.88999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>271.26</c:v>
+                  <c:v>277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135.63</c:v>
+                  <c:v>138.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-271.26</c:v>
+                  <c:v>-277.79000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-135.63</c:v>
+                  <c:v>-138.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26484,31 +26484,31 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>182.41</v>
+        <v>199.32</v>
       </c>
       <c r="C5">
-        <v>135.63</v>
+        <v>138.88999999999999</v>
       </c>
       <c r="D5">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E5">
-        <v>287.41000000000003</v>
+        <v>281.82</v>
       </c>
       <c r="F5">
-        <v>135.63</v>
+        <v>138.88999999999999</v>
       </c>
       <c r="G5">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H5">
-        <v>234.91</v>
+        <v>240.57</v>
       </c>
       <c r="I5">
-        <v>135.63</v>
+        <v>138.88999999999999</v>
       </c>
       <c r="J5">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -26516,31 +26516,31 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>-52.5</v>
+        <v>-41.25</v>
       </c>
       <c r="C6">
-        <v>271.26</v>
+        <v>277.79000000000002</v>
       </c>
       <c r="D6">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E6">
-        <v>52.5</v>
+        <v>41.25</v>
       </c>
       <c r="F6">
-        <v>271.26</v>
+        <v>277.79000000000002</v>
       </c>
       <c r="G6">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>271.26</v>
+        <v>277.79000000000002</v>
       </c>
       <c r="J6">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -26548,31 +26548,31 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>-287.41000000000003</v>
+        <v>-281.82</v>
       </c>
       <c r="C7">
-        <v>135.63</v>
+        <v>138.9</v>
       </c>
       <c r="D7">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E7">
-        <v>-182.41</v>
+        <v>-199.32</v>
       </c>
       <c r="F7">
-        <v>135.63</v>
+        <v>138.9</v>
       </c>
       <c r="G7">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H7">
-        <v>-234.91</v>
+        <v>-240.57</v>
       </c>
       <c r="I7">
-        <v>135.63</v>
+        <v>138.9</v>
       </c>
       <c r="J7">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -26580,31 +26580,31 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <v>-287.41000000000003</v>
+        <v>-281.82</v>
       </c>
       <c r="C8">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="D8">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E8">
-        <v>-182.41</v>
+        <v>-199.32</v>
       </c>
       <c r="F8">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="G8">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H8">
-        <v>-234.91</v>
+        <v>-240.57</v>
       </c>
       <c r="I8">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="J8">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -26612,31 +26612,31 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>-52.5</v>
+        <v>-41.25</v>
       </c>
       <c r="C9">
-        <v>-271.26</v>
+        <v>-277.79000000000002</v>
       </c>
       <c r="D9">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E9">
-        <v>52.5</v>
+        <v>41.25</v>
       </c>
       <c r="F9">
-        <v>-271.26</v>
+        <v>-277.79000000000002</v>
       </c>
       <c r="G9">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>-271.26</v>
+        <v>-277.79000000000002</v>
       </c>
       <c r="J9">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -26644,31 +26644,31 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>182.41</v>
+        <v>199.32</v>
       </c>
       <c r="C10">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="D10">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="E10">
-        <v>287.41000000000003</v>
+        <v>281.82</v>
       </c>
       <c r="F10">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="G10">
-        <v>-63.63</v>
+        <v>-89.66</v>
       </c>
       <c r="H10">
-        <v>234.91</v>
+        <v>240.57</v>
       </c>
       <c r="I10">
-        <v>-135.63</v>
+        <v>-138.9</v>
       </c>
       <c r="J10">
-        <v>-8.6300000000000008</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
+++ b/Design/Mechanical Design/Kinematics/Body Kinematics Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_vadeboncoeur\Documents\PlatformIO\Projects\Hexapod v3\Design\Mechanical Design\Kinematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F774419-B06F-4706-9248-32F96172EE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C874A6-B586-4B16-B099-F8793B5CA5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{80FB6A6E-4815-48DC-A8C5-309DA8648198}"/>
   </bookViews>
   <sheets>
     <sheet name="X" sheetId="1" r:id="rId1"/>
@@ -4640,19 +4640,19 @@
                   <c:v>281.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-27.5</c:v>
+                  <c:v>-41.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-254.32</c:v>
+                  <c:v>-265.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240.57</c:v>
+                  <c:v>232.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.75</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-213.07</c:v>
+                  <c:v>-215.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5439,22 +5439,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>268.07</c:v>
+                  <c:v>265.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>41.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-268.07</c:v>
+                  <c:v>-281.82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>226.82</c:v>
+                  <c:v>215.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>-8.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-226.82</c:v>
+                  <c:v>-232.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6241,22 +6241,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>254.32</c:v>
+                  <c:v>248.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.5</c:v>
+                  <c:v>24.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>-199.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>213.07</c:v>
+                  <c:v>199.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13.75</c:v>
+                  <c:v>-24.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-240.57</c:v>
+                  <c:v>-248.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7043,22 +7043,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>240.57</c:v>
+                  <c:v>232.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.75</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-213.07</c:v>
+                  <c:v>-215.82</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>281.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-27.5</c:v>
+                  <c:v>-41.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-254.32</c:v>
+                  <c:v>-265.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7845,19 +7845,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>213.07</c:v>
+                  <c:v>199.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-13.75</c:v>
+                  <c:v>-24.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-240.57</c:v>
+                  <c:v>-248.82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>254.32</c:v>
+                  <c:v>248.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27.5</c:v>
+                  <c:v>24.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-199.32</c:v>
@@ -8647,22 +8647,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>226.82</c:v>
+                  <c:v>215.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-8.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-226.82</c:v>
+                  <c:v>-232.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>268.07</c:v>
+                  <c:v>265.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>41.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-268.07</c:v>
+                  <c:v>-281.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30626,13 +30626,13 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AC5" t="s">
         <v>84</v>
       </c>
       <c r="AD5">
-        <v>268.07</v>
+        <v>265.32</v>
       </c>
       <c r="AE5">
         <v>138.88999999999999</v>
@@ -30641,22 +30641,22 @@
         <v>-89.66</v>
       </c>
       <c r="AG5">
-        <v>209.11</v>
+        <v>206.72</v>
       </c>
       <c r="AH5">
-        <v>-13.75</v>
+        <v>-12.38</v>
       </c>
       <c r="AI5">
         <v>-89.66</v>
       </c>
       <c r="AJ5">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="AK5">
-        <v>-0.54</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="AL5">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AN5">
         <v>2</v>
@@ -30665,13 +30665,13 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AQ5" t="s">
         <v>84</v>
       </c>
       <c r="AR5">
-        <v>254.32</v>
+        <v>248.82</v>
       </c>
       <c r="AS5">
         <v>138.88999999999999</v>
@@ -30680,22 +30680,22 @@
         <v>-89.66</v>
       </c>
       <c r="AU5">
-        <v>197.2</v>
+        <v>192.43</v>
       </c>
       <c r="AV5">
-        <v>-6.88</v>
+        <v>-4.13</v>
       </c>
       <c r="AW5">
         <v>-89.66</v>
       </c>
       <c r="AX5">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AY5">
-        <v>-0.6</v>
+        <v>-0.62</v>
       </c>
       <c r="AZ5">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="BB5">
         <v>3</v>
@@ -30704,13 +30704,13 @@
         <v>0</v>
       </c>
       <c r="BD5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BE5" t="s">
         <v>84</v>
       </c>
       <c r="BF5">
-        <v>240.57</v>
+        <v>232.32</v>
       </c>
       <c r="BG5">
         <v>138.88999999999999</v>
@@ -30719,22 +30719,22 @@
         <v>-89.66</v>
       </c>
       <c r="BI5">
-        <v>185.29</v>
+        <v>178.15</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="BK5">
         <v>-89.66</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BM5">
-        <v>-0.64</v>
+        <v>-0.67</v>
       </c>
       <c r="BN5">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="BP5">
         <v>4</v>
@@ -30743,13 +30743,13 @@
         <v>0</v>
       </c>
       <c r="BR5">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BS5" t="s">
         <v>84</v>
       </c>
       <c r="BT5">
-        <v>226.82</v>
+        <v>215.82</v>
       </c>
       <c r="BU5">
         <v>138.88999999999999</v>
@@ -30758,22 +30758,22 @@
         <v>-89.66</v>
       </c>
       <c r="BW5">
-        <v>173.38</v>
+        <v>163.86</v>
       </c>
       <c r="BX5">
-        <v>6.88</v>
+        <v>12.38</v>
       </c>
       <c r="BY5">
         <v>-89.66</v>
       </c>
       <c r="BZ5">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="CA5">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="CB5">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="CD5">
         <v>5</v>
@@ -30782,13 +30782,13 @@
         <v>0</v>
       </c>
       <c r="CF5">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="CG5" t="s">
         <v>84</v>
       </c>
       <c r="CH5">
-        <v>213.07</v>
+        <v>199.32</v>
       </c>
       <c r="CI5">
         <v>138.88999999999999</v>
@@ -30797,22 +30797,22 @@
         <v>-89.66</v>
       </c>
       <c r="CK5">
-        <v>161.47</v>
+        <v>149.57</v>
       </c>
       <c r="CL5">
-        <v>13.75</v>
+        <v>20.62</v>
       </c>
       <c r="CM5">
         <v>-89.66</v>
       </c>
       <c r="CN5">
-        <v>0.08</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="CO5">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="CP5">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6" spans="1:94" x14ac:dyDescent="0.25">
@@ -30853,13 +30853,13 @@
         <v>4</v>
       </c>
       <c r="N6">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O6" t="s">
         <v>84</v>
       </c>
       <c r="P6">
-        <v>-27.5</v>
+        <v>-41.25</v>
       </c>
       <c r="Q6">
         <v>-277.79000000000002</v>
@@ -30871,19 +30871,19 @@
         <v>185.29</v>
       </c>
       <c r="T6">
-        <v>-27.5</v>
+        <v>-41.25</v>
       </c>
       <c r="U6">
         <v>-89.66</v>
       </c>
       <c r="V6">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="W6">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="X6">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -30904,7 +30904,7 @@
         <v>-277.79000000000002</v>
       </c>
       <c r="AF6">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="AG6">
         <v>185.29</v>
@@ -30913,16 +30913,16 @@
         <v>41.25</v>
       </c>
       <c r="AI6">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="AJ6">
         <v>0.22</v>
       </c>
       <c r="AK6">
-        <v>-0.63</v>
+        <v>-1.24</v>
       </c>
       <c r="AL6">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AN6">
         <v>2</v>
@@ -30931,13 +30931,13 @@
         <v>4</v>
       </c>
       <c r="AP6">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AQ6" t="s">
         <v>84</v>
       </c>
       <c r="AR6">
-        <v>27.5</v>
+        <v>24.75</v>
       </c>
       <c r="AS6">
         <v>-277.79000000000002</v>
@@ -30949,19 +30949,19 @@
         <v>185.29</v>
       </c>
       <c r="AV6">
-        <v>27.5</v>
+        <v>24.75</v>
       </c>
       <c r="AW6">
         <v>-89.66</v>
       </c>
       <c r="AX6">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AY6">
         <v>-0.64</v>
       </c>
       <c r="AZ6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BB6">
         <v>3</v>
@@ -30970,13 +30970,13 @@
         <v>4</v>
       </c>
       <c r="BD6">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BE6" t="s">
         <v>84</v>
       </c>
       <c r="BF6">
-        <v>13.75</v>
+        <v>8.25</v>
       </c>
       <c r="BG6">
         <v>-277.79000000000002</v>
@@ -30988,13 +30988,13 @@
         <v>185.29</v>
       </c>
       <c r="BJ6">
-        <v>13.75</v>
+        <v>8.25</v>
       </c>
       <c r="BK6">
         <v>-89.66</v>
       </c>
       <c r="BL6">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="BM6">
         <v>-0.64</v>
@@ -31009,13 +31009,13 @@
         <v>4</v>
       </c>
       <c r="BR6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BS6" t="s">
         <v>84</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>-8.25</v>
       </c>
       <c r="BU6">
         <v>-277.79000000000002</v>
@@ -31027,13 +31027,13 @@
         <v>185.29</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>-8.25</v>
       </c>
       <c r="BY6">
         <v>-89.66</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="CA6">
         <v>-0.64</v>
@@ -31048,13 +31048,13 @@
         <v>4</v>
       </c>
       <c r="CF6">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="CG6" t="s">
         <v>84</v>
       </c>
       <c r="CH6">
-        <v>-13.75</v>
+        <v>-24.75</v>
       </c>
       <c r="CI6">
         <v>-277.79000000000002</v>
@@ -31066,19 +31066,19 @@
         <v>185.29</v>
       </c>
       <c r="CL6">
-        <v>-13.75</v>
+        <v>-24.75</v>
       </c>
       <c r="CM6">
         <v>-89.66</v>
       </c>
       <c r="CN6">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.13</v>
       </c>
       <c r="CO6">
         <v>-0.64</v>
       </c>
       <c r="CP6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7" spans="1:94" x14ac:dyDescent="0.25">
@@ -31119,13 +31119,13 @@
         <v>2</v>
       </c>
       <c r="N7">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="s">
         <v>84</v>
       </c>
       <c r="P7">
-        <v>-254.32</v>
+        <v>-265.32</v>
       </c>
       <c r="Q7">
         <v>138.9</v>
@@ -31134,22 +31134,22 @@
         <v>-89.66</v>
       </c>
       <c r="S7">
-        <v>197.2</v>
+        <v>206.72</v>
       </c>
       <c r="T7">
-        <v>6.88</v>
+        <v>12.38</v>
       </c>
       <c r="U7">
         <v>-89.66</v>
       </c>
       <c r="V7">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="W7">
-        <v>-0.6</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="X7">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="Z7">
         <v>1</v>
@@ -31158,13 +31158,13 @@
         <v>2</v>
       </c>
       <c r="AB7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="s">
         <v>84</v>
       </c>
       <c r="AD7">
-        <v>-268.07</v>
+        <v>-281.82</v>
       </c>
       <c r="AE7">
         <v>138.9</v>
@@ -31173,22 +31173,22 @@
         <v>-89.66</v>
       </c>
       <c r="AG7">
-        <v>209.11</v>
+        <v>221.01</v>
       </c>
       <c r="AH7">
-        <v>13.75</v>
+        <v>20.63</v>
       </c>
       <c r="AI7">
         <v>-89.66</v>
       </c>
       <c r="AJ7">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="AK7">
-        <v>-0.54</v>
+        <v>-0.48</v>
       </c>
       <c r="AL7">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AN7">
         <v>2</v>
@@ -31209,7 +31209,7 @@
         <v>138.9</v>
       </c>
       <c r="AT7">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="AU7">
         <v>149.57</v>
@@ -31218,16 +31218,16 @@
         <v>-20.62</v>
       </c>
       <c r="AW7">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="AX7">
         <v>-0.14000000000000001</v>
       </c>
       <c r="AY7">
-        <v>-0.73</v>
+        <v>-1.6</v>
       </c>
       <c r="AZ7">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
       <c r="BB7">
         <v>3</v>
@@ -31236,13 +31236,13 @@
         <v>2</v>
       </c>
       <c r="BD7">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="BE7" t="s">
         <v>84</v>
       </c>
       <c r="BF7">
-        <v>-213.07</v>
+        <v>-215.82</v>
       </c>
       <c r="BG7">
         <v>138.9</v>
@@ -31251,10 +31251,10 @@
         <v>-89.66</v>
       </c>
       <c r="BI7">
-        <v>161.47</v>
+        <v>163.86</v>
       </c>
       <c r="BJ7">
-        <v>-13.75</v>
+        <v>-12.37</v>
       </c>
       <c r="BK7">
         <v>-89.66</v>
@@ -31263,10 +31263,10 @@
         <v>-0.08</v>
       </c>
       <c r="BM7">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="BN7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BP7">
         <v>4</v>
@@ -31275,13 +31275,13 @@
         <v>2</v>
       </c>
       <c r="BR7">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BS7" t="s">
         <v>84</v>
       </c>
       <c r="BT7">
-        <v>-226.82</v>
+        <v>-232.32</v>
       </c>
       <c r="BU7">
         <v>138.9</v>
@@ -31290,22 +31290,22 @@
         <v>-89.66</v>
       </c>
       <c r="BW7">
-        <v>173.38</v>
+        <v>178.15</v>
       </c>
       <c r="BX7">
-        <v>-6.87</v>
+        <v>-4.12</v>
       </c>
       <c r="BY7">
         <v>-89.66</v>
       </c>
       <c r="BZ7">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="CA7">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="CB7">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CD7">
         <v>5</v>
@@ -31314,13 +31314,13 @@
         <v>2</v>
       </c>
       <c r="CF7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="CG7" t="s">
         <v>84</v>
       </c>
       <c r="CH7">
-        <v>-240.57</v>
+        <v>-248.82</v>
       </c>
       <c r="CI7">
         <v>138.9</v>
@@ -31329,22 +31329,22 @@
         <v>-89.66</v>
       </c>
       <c r="CK7">
-        <v>185.29</v>
+        <v>192.43</v>
       </c>
       <c r="CL7">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="CM7">
         <v>-89.66</v>
       </c>
       <c r="CN7">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CO7">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="CP7">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8" spans="1:94" x14ac:dyDescent="0.25">
@@ -31385,13 +31385,13 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="s">
         <v>84</v>
       </c>
       <c r="P8">
-        <v>240.57</v>
+        <v>232.32</v>
       </c>
       <c r="Q8">
         <v>-138.9</v>
@@ -31400,22 +31400,22 @@
         <v>-89.66</v>
       </c>
       <c r="S8">
-        <v>185.29</v>
+        <v>178.15</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>-4.13</v>
       </c>
       <c r="U8">
         <v>-89.66</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="W8">
-        <v>-0.64</v>
+        <v>-0.67</v>
       </c>
       <c r="X8">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Z8">
         <v>1</v>
@@ -31424,13 +31424,13 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AC8" t="s">
         <v>84</v>
       </c>
       <c r="AD8">
-        <v>226.82</v>
+        <v>215.82</v>
       </c>
       <c r="AE8">
         <v>-138.9</v>
@@ -31439,22 +31439,22 @@
         <v>-89.66</v>
       </c>
       <c r="AG8">
-        <v>173.38</v>
+        <v>163.86</v>
       </c>
       <c r="AH8">
-        <v>-6.88</v>
+        <v>-12.38</v>
       </c>
       <c r="AI8">
         <v>-89.66</v>
       </c>
       <c r="AJ8">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="AK8">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="AL8">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AN8">
         <v>2</v>
@@ -31463,13 +31463,13 @@
         <v>5</v>
       </c>
       <c r="AP8">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="s">
         <v>84</v>
       </c>
       <c r="AR8">
-        <v>213.07</v>
+        <v>199.32</v>
       </c>
       <c r="AS8">
         <v>-138.9</v>
@@ -31478,22 +31478,22 @@
         <v>-89.66</v>
       </c>
       <c r="AU8">
-        <v>161.47</v>
+        <v>149.57</v>
       </c>
       <c r="AV8">
-        <v>-13.75</v>
+        <v>-20.63</v>
       </c>
       <c r="AW8">
         <v>-89.66</v>
       </c>
       <c r="AX8">
-        <v>-0.08</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="AY8">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="AZ8">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="BB8">
         <v>3</v>
@@ -31514,7 +31514,7 @@
         <v>-138.9</v>
       </c>
       <c r="BH8">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="BI8">
         <v>221.01</v>
@@ -31523,16 +31523,16 @@
         <v>20.62</v>
       </c>
       <c r="BK8">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="BL8">
         <v>0.09</v>
       </c>
       <c r="BM8">
-        <v>-0.48</v>
+        <v>-0.99</v>
       </c>
       <c r="BN8">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="BP8">
         <v>4</v>
@@ -31541,13 +31541,13 @@
         <v>5</v>
       </c>
       <c r="BR8">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="BS8" t="s">
         <v>84</v>
       </c>
       <c r="BT8">
-        <v>268.07</v>
+        <v>265.32</v>
       </c>
       <c r="BU8">
         <v>-138.9</v>
@@ -31556,22 +31556,22 @@
         <v>-89.66</v>
       </c>
       <c r="BW8">
-        <v>209.11</v>
+        <v>206.72</v>
       </c>
       <c r="BX8">
-        <v>13.75</v>
+        <v>12.37</v>
       </c>
       <c r="BY8">
         <v>-89.66</v>
       </c>
       <c r="BZ8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="CA8">
-        <v>-0.54</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="CB8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CD8">
         <v>5</v>
@@ -31580,13 +31580,13 @@
         <v>5</v>
       </c>
       <c r="CF8">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="CG8" t="s">
         <v>84</v>
       </c>
       <c r="CH8">
-        <v>254.32</v>
+        <v>248.82</v>
       </c>
       <c r="CI8">
         <v>-138.9</v>
@@ -31595,22 +31595,22 @@
         <v>-89.66</v>
       </c>
       <c r="CK8">
-        <v>197.2</v>
+        <v>192.43</v>
       </c>
       <c r="CL8">
-        <v>6.87</v>
+        <v>4.12</v>
       </c>
       <c r="CM8">
         <v>-89.66</v>
       </c>
       <c r="CN8">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="CO8">
-        <v>-0.6</v>
+        <v>-0.62</v>
       </c>
       <c r="CP8">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="9" spans="1:94" x14ac:dyDescent="0.25">
@@ -31651,13 +31651,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O9" t="s">
         <v>84</v>
       </c>
       <c r="P9">
-        <v>13.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q9">
         <v>277.79000000000002</v>
@@ -31669,13 +31669,13 @@
         <v>185.29</v>
       </c>
       <c r="T9">
-        <v>-13.75</v>
+        <v>-8.25</v>
       </c>
       <c r="U9">
         <v>-89.66</v>
       </c>
       <c r="V9">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.04</v>
       </c>
       <c r="W9">
         <v>-0.64</v>
@@ -31690,13 +31690,13 @@
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AC9" t="s">
         <v>84</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>-8.25</v>
       </c>
       <c r="AE9">
         <v>277.79000000000002</v>
@@ -31708,13 +31708,13 @@
         <v>185.29</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AI9">
         <v>-89.66</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AK9">
         <v>-0.64</v>
@@ -31729,13 +31729,13 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AQ9" t="s">
         <v>84</v>
       </c>
       <c r="AR9">
-        <v>-13.75</v>
+        <v>-24.75</v>
       </c>
       <c r="AS9">
         <v>277.79000000000002</v>
@@ -31747,19 +31747,19 @@
         <v>185.29</v>
       </c>
       <c r="AV9">
-        <v>13.75</v>
+        <v>24.75</v>
       </c>
       <c r="AW9">
         <v>-89.66</v>
       </c>
       <c r="AX9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.13</v>
       </c>
       <c r="AY9">
         <v>-0.64</v>
       </c>
       <c r="AZ9">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BB9">
         <v>3</v>
@@ -31768,13 +31768,13 @@
         <v>1</v>
       </c>
       <c r="BD9">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BE9" t="s">
         <v>84</v>
       </c>
       <c r="BF9">
-        <v>-27.5</v>
+        <v>-41.25</v>
       </c>
       <c r="BG9">
         <v>277.79000000000002</v>
@@ -31786,19 +31786,19 @@
         <v>185.29</v>
       </c>
       <c r="BJ9">
-        <v>27.5</v>
+        <v>41.25</v>
       </c>
       <c r="BK9">
         <v>-89.66</v>
       </c>
       <c r="BL9">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="BM9">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="BN9">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BP9">
         <v>4</v>
@@ -31819,7 +31819,7 @@
         <v>277.79000000000002</v>
       </c>
       <c r="BV9">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="BW9">
         <v>185.29</v>
@@ -31828,16 +31828,16 @@
         <v>-41.25</v>
       </c>
       <c r="BY9">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="BZ9">
         <v>-0.22</v>
       </c>
       <c r="CA9">
-        <v>-0.63</v>
+        <v>-1.24</v>
       </c>
       <c r="CB9">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="CD9">
         <v>5</v>
@@ -31846,13 +31846,13 @@
         <v>1</v>
       </c>
       <c r="CF9">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="CG9" t="s">
         <v>84</v>
       </c>
       <c r="CH9">
-        <v>27.5</v>
+        <v>24.75</v>
       </c>
       <c r="CI9">
         <v>277.79000000000002</v>
@@ -31864,19 +31864,19 @@
         <v>185.29</v>
       </c>
       <c r="CL9">
-        <v>-27.5</v>
+        <v>-24.75</v>
       </c>
       <c r="CM9">
         <v>-89.66</v>
       </c>
       <c r="CN9">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="CO9">
         <v>-0.64</v>
       </c>
       <c r="CP9">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="10" spans="1:94" x14ac:dyDescent="0.25">
@@ -31917,13 +31917,13 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="O10" t="s">
         <v>84</v>
       </c>
       <c r="P10">
-        <v>-213.07</v>
+        <v>-215.82</v>
       </c>
       <c r="Q10">
         <v>-138.9</v>
@@ -31932,10 +31932,10 @@
         <v>-89.66</v>
       </c>
       <c r="S10">
-        <v>161.47</v>
+        <v>163.86</v>
       </c>
       <c r="T10">
-        <v>13.75</v>
+        <v>12.38</v>
       </c>
       <c r="U10">
         <v>-89.66</v>
@@ -31944,10 +31944,10 @@
         <v>0.08</v>
       </c>
       <c r="W10">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="X10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -31956,13 +31956,13 @@
         <v>3</v>
       </c>
       <c r="AB10">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AC10" t="s">
         <v>84</v>
       </c>
       <c r="AD10">
-        <v>-226.82</v>
+        <v>-232.32</v>
       </c>
       <c r="AE10">
         <v>-138.9</v>
@@ -31971,22 +31971,22 @@
         <v>-89.66</v>
       </c>
       <c r="AG10">
-        <v>173.38</v>
+        <v>178.15</v>
       </c>
       <c r="AH10">
-        <v>6.88</v>
+        <v>4.13</v>
       </c>
       <c r="AI10">
         <v>-89.66</v>
       </c>
       <c r="AJ10">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="AK10">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AL10">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AN10">
         <v>2</v>
@@ -31995,13 +31995,13 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ10" t="s">
         <v>84</v>
       </c>
       <c r="AR10">
-        <v>-240.57</v>
+        <v>-248.82</v>
       </c>
       <c r="AS10">
         <v>-138.9</v>
@@ -32010,22 +32010,22 @@
         <v>-89.66</v>
       </c>
       <c r="AU10">
-        <v>185.29</v>
+        <v>192.43</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>-4.12</v>
       </c>
       <c r="AW10">
         <v>-89.66</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AY10">
-        <v>-0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="AZ10">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BB10">
         <v>3</v>
@@ -32034,13 +32034,13 @@
         <v>3</v>
       </c>
       <c r="BD10">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BE10" t="s">
         <v>84</v>
       </c>
       <c r="BF10">
-        <v>-254.32</v>
+        <v>-265.32</v>
       </c>
       <c r="BG10">
         <v>-138.9</v>
@@ -32049,22 +32049,22 @@
         <v>-89.66</v>
       </c>
       <c r="BI10">
-        <v>197.2</v>
+        <v>206.72</v>
       </c>
       <c r="BJ10">
-        <v>-6.87</v>
+        <v>-12.37</v>
       </c>
       <c r="BK10">
         <v>-89.66</v>
       </c>
       <c r="BL10">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="BM10">
-        <v>-0.6</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="BN10">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BP10">
         <v>4</v>
@@ -32073,13 +32073,13 @@
         <v>3</v>
       </c>
       <c r="BR10">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BS10" t="s">
         <v>84</v>
       </c>
       <c r="BT10">
-        <v>-268.07</v>
+        <v>-281.82</v>
       </c>
       <c r="BU10">
         <v>-138.9</v>
@@ -32088,22 +32088,22 @@
         <v>-89.66</v>
       </c>
       <c r="BW10">
-        <v>209.11</v>
+        <v>221.01</v>
       </c>
       <c r="BX10">
-        <v>-13.75</v>
+        <v>-20.62</v>
       </c>
       <c r="BY10">
         <v>-89.66</v>
       </c>
       <c r="BZ10">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.09</v>
       </c>
       <c r="CA10">
-        <v>-0.54</v>
+        <v>-0.48</v>
       </c>
       <c r="CB10">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="CD10">
         <v>5</v>
@@ -32124,7 +32124,7 @@
         <v>-138.9</v>
       </c>
       <c r="CJ10">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="CK10">
         <v>149.57</v>
@@ -32133,16 +32133,16 @@
         <v>20.63</v>
       </c>
       <c r="CM10">
-        <v>-89.66</v>
+        <v>-34.659999999999997</v>
       </c>
       <c r="CN10">
         <v>0.14000000000000001</v>
       </c>
       <c r="CO10">
-        <v>-0.73</v>
+        <v>-1.6</v>
       </c>
       <c r="CP10">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
